--- a/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 4,45</t>
+          <t>-7,65; 4,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 4,73</t>
+          <t>-7,5; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 7,0</t>
+          <t>-6,25; 7,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 12,4</t>
+          <t>-3,17; 12,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,21; -0,54</t>
+          <t>-11,14; -0,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,35</t>
+          <t>-10,86; -0,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,37</t>
+          <t>-3,21; 6,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,39</t>
+          <t>-7,67; 0,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,38</t>
+          <t>-6,96; 1,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-81,45; 148,98</t>
+          <t>-79,13; 253,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 156,95</t>
+          <t>-85,85; 243,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,26; 256,75</t>
+          <t>-69,34; 279,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,4; 337,38</t>
+          <t>-40,4; 346,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,98</t>
+          <t>-100,0; 37,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,04; 27,17</t>
+          <t>-100,0; 27,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,92; 174,71</t>
+          <t>-39,85; 142,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,79; 21,86</t>
+          <t>-83,99; 26,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,69; 43,27</t>
+          <t>-75,45; 28,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,17</t>
+          <t>-4,07; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 6,09</t>
+          <t>-4,52; 5,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,85</t>
+          <t>-5,19; 6,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,39</t>
+          <t>-9,84; -0,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,15</t>
+          <t>-7,9; 3,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -0,3</t>
+          <t>-9,81; -0,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,73</t>
+          <t>-6,04; 1,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,92</t>
+          <t>-5,02; 2,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,4</t>
+          <t>-6,5; 0,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,86; 189,4</t>
+          <t>-52,54; 174,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,36; 182,04</t>
+          <t>-55,16; 156,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,37; 189,0</t>
+          <t>-65,23; 172,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,8; 6,6</t>
+          <t>-88,74; 7,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,22; 72,5</t>
+          <t>-75,23; 70,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,02; 12,94</t>
+          <t>-88,65; -0,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 32,79</t>
+          <t>-64,64; 25,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; 60,29</t>
+          <t>-55,74; 48,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-71,27; 13,9</t>
+          <t>-73,13; 17,82</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 12,84</t>
+          <t>-0,2; 12,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 5,26</t>
+          <t>-4,73; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 6,21</t>
+          <t>-3,99; 6,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 4,33</t>
+          <t>-9,38; 4,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 0,61</t>
+          <t>-11,97; 0,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 1,31</t>
+          <t>-11,64; 1,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 5,83</t>
+          <t>-3,41; 6,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 0,92</t>
+          <t>-7,18; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,16</t>
+          <t>-6,37; 2,14</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 1102,02</t>
+          <t>-21,16; 1044,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,55; 438,18</t>
+          <t>-80,4; 442,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 508,76</t>
+          <t>-77,88; 482,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 90,29</t>
+          <t>-74,11; 74,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,1; 27,97</t>
+          <t>-90,89; 45,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,57; 40,96</t>
+          <t>-84,65; 42,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 127,38</t>
+          <t>-42,96; 152,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,26; 30,64</t>
+          <t>-76,17; 30,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,24; 55,66</t>
+          <t>-70,17; 54,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 2,29</t>
+          <t>-8,3; 2,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 4,17</t>
+          <t>-6,86; 4,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,02; -0,2</t>
+          <t>-10,09; -0,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 4,4</t>
+          <t>-5,61; 4,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,35</t>
+          <t>-5,81; 3,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 3,56</t>
+          <t>-6,06; 3,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,29</t>
+          <t>-5,99; 1,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,94</t>
+          <t>-4,49; 3,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 0,32</t>
+          <t>-6,49; 0,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,99; 91,16</t>
+          <t>-86,33; 93,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 103,56</t>
+          <t>-70,27; 141,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,57; 43,26</t>
+          <t>-100,0; 14,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,85; 240,16</t>
+          <t>-82,7; 258,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-70,49; 287,45</t>
+          <t>-80,09; 196,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,94; 212,31</t>
+          <t>-85,26; 158,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,74; 71,91</t>
+          <t>-75,25; 65,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,95; 81,27</t>
+          <t>-62,15; 97,74</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 20,8</t>
+          <t>-81,31; 10,11</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,54</t>
+          <t>-2,28; 3,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 2,24</t>
+          <t>-3,43; 2,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,02</t>
+          <t>-3,96; 1,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 1,71</t>
+          <t>-4,17; 1,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; -0,43</t>
+          <t>-5,9; -0,39</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,55; -1,31</t>
+          <t>-6,42; -1,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,96</t>
+          <t>-2,43; 1,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,04</t>
+          <t>-3,89; 0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,66</t>
+          <t>-4,42; -0,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 76,42</t>
+          <t>-33,09; 83,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,75; 51,72</t>
+          <t>-45,9; 51,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 48,5</t>
+          <t>-54,1; 41,55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 29,63</t>
+          <t>-49,19; 37,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,79; -6,4</t>
+          <t>-67,6; -3,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,94; -23,52</t>
+          <t>-74,75; -25,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 34,52</t>
+          <t>-33,09; 32,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,74; 1,12</t>
+          <t>-51,35; 0,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,68; -11,61</t>
+          <t>-57,92; -11,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 4,9</t>
+          <t>-7,4; 4,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 5,26</t>
+          <t>-8,21; 4,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 7,58</t>
+          <t>-6,42; 7,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 12,32</t>
+          <t>-3,5; 12,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; -0,47</t>
+          <t>-10,99; -0,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -0,2</t>
+          <t>-11,37; -0,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 6,47</t>
+          <t>-3,25; 6,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,43</t>
+          <t>-7,83; 0,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 1,25</t>
+          <t>-7,06; 1,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 253,91</t>
+          <t>-78,68; 178,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-85,85; 243,31</t>
+          <t>-86,76; 163,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,34; 279,71</t>
+          <t>-69,97; 264,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,4; 346,04</t>
+          <t>-39,18; 359,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,51</t>
+          <t>-100,0; 60,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,04</t>
+          <t>-95,71; 23,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,85; 142,16</t>
+          <t>-40,34; 155,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,99; 26,75</t>
+          <t>-84,81; 21,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 28,54</t>
+          <t>-75,33; 40,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 6,2</t>
+          <t>-4,57; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,55</t>
+          <t>-4,95; 5,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,24</t>
+          <t>-5,19; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; -0,2</t>
+          <t>-10,26; -0,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 3,33</t>
+          <t>-8,39; 2,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,81; -0,83</t>
+          <t>-10,65; -0,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,34</t>
+          <t>-6,04; 1,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 2,42</t>
+          <t>-4,96; 2,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,55</t>
+          <t>-6,57; 0,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,54; 174,16</t>
+          <t>-53,88; 172,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,16; 156,53</t>
+          <t>-55,79; 158,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 172,81</t>
+          <t>-64,8; 165,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,74; 7,02</t>
+          <t>-88,95; 8,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,23; 70,08</t>
+          <t>-75,7; 63,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,65; -0,52</t>
+          <t>-88,73; 4,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 25,96</t>
+          <t>-63,95; 31,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 48,12</t>
+          <t>-56,33; 46,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,13; 17,82</t>
+          <t>-69,63; 21,2</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 12,78</t>
+          <t>-0,14; 12,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,26</t>
+          <t>-5,07; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 6,11</t>
+          <t>-4,55; 5,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 4,0</t>
+          <t>-9,14; 4,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 0,64</t>
+          <t>-12,09; 0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 1,59</t>
+          <t>-11,0; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 6,42</t>
+          <t>-3,25; 6,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 0,9</t>
+          <t>-7,35; 0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,14</t>
+          <t>-6,77; 1,86</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 1044,39</t>
+          <t>-29,75; 1058,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 442,74</t>
+          <t>-81,73; 531,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,88; 482,42</t>
+          <t>-78,65; 397,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,11; 74,37</t>
+          <t>-75,58; 87,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-90,89; 45,48</t>
+          <t>-91,21; 42,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,65; 42,2</t>
+          <t>-85,29; 37,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 152,84</t>
+          <t>-38,49; 139,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,17; 30,22</t>
+          <t>-76,98; 30,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-70,17; 54,97</t>
+          <t>-71,65; 46,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 2,74</t>
+          <t>-8,49; 2,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 4,61</t>
+          <t>-6,99; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,43</t>
+          <t>-10,25; -0,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 4,85</t>
+          <t>-5,64; 4,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 3,86</t>
+          <t>-5,52; 3,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,15</t>
+          <t>-6,14; 2,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 1,85</t>
+          <t>-5,9; 1,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 3,25</t>
+          <t>-4,71; 2,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,0</t>
+          <t>-6,49; 0,16</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 93,57</t>
+          <t>-88,64; 82,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,27; 141,49</t>
+          <t>-71,81; 139,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,94</t>
+          <t>-93,86; 28,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-82,7; 258,66</t>
+          <t>-81,44; 247,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-80,09; 196,74</t>
+          <t>-76,89; 249,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,26; 158,75</t>
+          <t>-83,77; 229,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 65,67</t>
+          <t>-73,49; 71,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,15; 97,74</t>
+          <t>-59,7; 89,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,31; 10,11</t>
+          <t>-81,37; 13,98</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,65</t>
+          <t>-2,38; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,15</t>
+          <t>-3,13; 2,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 1,8</t>
+          <t>-3,75; 1,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,86</t>
+          <t>-4,42; 1,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,39</t>
+          <t>-6,0; -0,5</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -1,56</t>
+          <t>-6,63; -1,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,68</t>
+          <t>-2,59; 1,51</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,02</t>
+          <t>-3,76; 0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,68</t>
+          <t>-4,36; -0,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 83,34</t>
+          <t>-33,03; 91,8</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 51,23</t>
+          <t>-44,12; 57,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 41,55</t>
+          <t>-50,56; 44,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 37,15</t>
+          <t>-51,94; 30,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,6; -3,83</t>
+          <t>-69,38; -7,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,75; -25,44</t>
+          <t>-75,33; -20,99</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 32,03</t>
+          <t>-35,27; 27,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 0,23</t>
+          <t>-49,38; 2,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-57,92; -11,27</t>
+          <t>-58,21; -10,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,07</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-5,11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,03</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,21</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,07</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,88</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,57</t>
+          <t>-2,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 4,69</t>
+          <t>-2,96; 12,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 4,56</t>
+          <t>-11,21; -0,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 7,25</t>
+          <t>-10,89; -0,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 12,66</t>
+          <t>-7,55; 4,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -0,02</t>
+          <t>-8,18; 4,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,37; -0,48</t>
+          <t>-6,31; 6,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,77</t>
+          <t>-3,07; 7,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,54</t>
+          <t>-8,0; 0,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 1,52</t>
+          <t>-6,67; 1,39</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>61,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-72,95%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-73,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-21,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-31,56%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>61,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-72,95%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-70,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-38,37%</t>
+          <t>-38,86%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,68; 178,86</t>
+          <t>-38,4; 337,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-86,76; 163,36</t>
+          <t>-100,0; 37,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,97; 264,87</t>
+          <t>-95,38; 17,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 359,99</t>
+          <t>-81,45; 148,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,24</t>
+          <t>-87,49; 156,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,71; 23,7</t>
+          <t>-71,95; 255,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,34; 155,59</t>
+          <t>-39,92; 174,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,81; 21,01</t>
+          <t>-84,79; 21,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-75,33; 40,09</t>
+          <t>-74,37; 40,78</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,01</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,36</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,95</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,36</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,92</t>
+          <t>-2,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,99</t>
+          <t>-3,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 6,26</t>
+          <t>-10,27; -0,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 5,63</t>
+          <t>-7,94; 3,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,55</t>
+          <t>-10,24; -0,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,26; -0,44</t>
+          <t>-4,11; 6,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 2,67</t>
+          <t>-4,72; 6,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,65; -0,85</t>
+          <t>-6,56; 2,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 1,28</t>
+          <t>-5,58; 1,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,64</t>
+          <t>-4,83; 2,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 0,42</t>
+          <t>-6,97; -0,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-63,74%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-30,03%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-62,96%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>15,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,41%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-63,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-30,03%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-62,54%</t>
+          <t>-34,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-42,37%</t>
+          <t>-51,58%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 172,15</t>
+          <t>-88,8; 6,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,79; 158,8</t>
+          <t>-75,22; 72,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,8; 165,06</t>
+          <t>-87,79; 12,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,95; 8,08</t>
+          <t>-52,86; 189,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,7; 63,42</t>
+          <t>-57,36; 182,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,73; 4,66</t>
+          <t>-74,3; 74,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 31,97</t>
+          <t>-63,35; 32,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,33; 46,79</t>
+          <t>-55,37; 60,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,63; 21,2</t>
+          <t>-75,73; -5,13</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,41</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,72</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,41</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,75</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-1,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 12,76</t>
+          <t>-9,32; 4,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,19</t>
+          <t>-11,66; 0,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 5,79</t>
+          <t>-11,36; 1,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,43</t>
+          <t>-0,04; 12,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 0,54</t>
+          <t>-4,82; 5,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 1,08</t>
+          <t>-3,21; 7,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,18</t>
+          <t>-3,37; 5,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,84</t>
+          <t>-6,82; 0,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,86</t>
+          <t>-5,75; 2,62</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-25,11%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-59,88%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-52,26%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>160,29%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36,1%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-25,11%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-59,88%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-52,56%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-28,95%</t>
+          <t>-24,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 1058,96</t>
+          <t>-73,53; 90,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,73; 531,59</t>
+          <t>-91,1; 27,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,65; 397,8</t>
+          <t>-83,72; 46,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-75,58; 87,87</t>
+          <t>-17,46; 1102,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-91,21; 42,34</t>
+          <t>-82,55; 438,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 37,52</t>
+          <t>-67,22; 615,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 139,79</t>
+          <t>-39,04; 127,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-76,98; 30,94</t>
+          <t>-76,26; 30,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-71,65; 46,58</t>
+          <t>-66,75; 61,94</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,64</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-4,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>-3,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 2,26</t>
+          <t>-5,46; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 4,47</t>
+          <t>-4,93; 4,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,25; -0,55</t>
+          <t>-5,81; 3,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 4,88</t>
+          <t>-8,6; 2,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 3,68</t>
+          <t>-7,24; 4,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,8</t>
+          <t>-10,04; -0,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 1,96</t>
+          <t>-5,44; 2,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 2,98</t>
+          <t>-4,91; 2,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,16</t>
+          <t>-6,96; 0,1</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-11,37%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-12,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-29,65%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-46,02%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-13,85%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-71,56%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-11,37%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-12,73%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-25,92%</t>
+          <t>-72,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-52,34%</t>
+          <t>-55,11%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,64; 82,84</t>
+          <t>-80,85; 240,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 139,57</t>
+          <t>-70,49; 287,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-93,86; 28,41</t>
+          <t>-85,86; 202,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 247,15</t>
+          <t>-88,99; 91,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,89; 249,41</t>
+          <t>-76,36; 103,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,77; 229,65</t>
+          <t>-94,48; 32,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-73,49; 71,87</t>
+          <t>-72,74; 71,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 89,39</t>
+          <t>-62,95; 81,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 13,98</t>
+          <t>-83,63; 9,47</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,35</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-3,16</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-3,95</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,57</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,15</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-3,16</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,86</t>
+          <t>-1,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-2,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 3,68</t>
+          <t>-4,2; 1,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 2,41</t>
+          <t>-5,93; -0,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,74</t>
+          <t>-6,65; -1,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,56</t>
+          <t>-2,42; 3,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,5</t>
+          <t>-3,16; 2,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -1,3</t>
+          <t>-4,16; 1,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 1,51</t>
+          <t>-2,47; 1,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,04</t>
+          <t>-4,08; 0,04</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,63</t>
+          <t>-4,5; -0,83</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-19,07%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-44,67%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-55,8%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-9,68%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-19,74%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-19,07%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-44,67%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-54,51%</t>
+          <t>-25,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-40,08%</t>
+          <t>-42,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,03; 91,8</t>
+          <t>-48,69; 29,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,12; 57,82</t>
+          <t>-69,79; -6,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,56; 44,19</t>
+          <t>-75,65; -24,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 30,27</t>
+          <t>-33,59; 76,42</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -7,03</t>
+          <t>-44,75; 51,72</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-75,33; -20,99</t>
+          <t>-56,75; 33,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 27,65</t>
+          <t>-32,88; 34,52</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-49,38; 2,17</t>
+          <t>-52,74; 1,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,21; -10,17</t>
+          <t>-60,42; -14,97</t>
         </is>
       </c>
     </row>
